--- a/Simulation_study/sim300_fmd/simulated_motifs_analysis.xlsx
+++ b/Simulation_study/sim300_fmd/simulated_motifs_analysis.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,6 +375,11 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Initialization</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -384,43 +389,58 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>0.0004935179472228385</v>
+        <v>1.01580091787753</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>0.001232033953126148</v>
+        <v>0.483927998760135</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>15</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0.0005428179851395422</v>
+        <v>0.7719363344444085</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>15</v>
@@ -429,26 +449,36 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>0.0009506433246388758</v>
+        <v>0.9506433246388758</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0.0007719363344444085</v>
+        <v>0.4725946426520827</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -457,12 +487,17 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>0.0008055585344498605</v>
+        <v>0.6486905807533534</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>16</v>
@@ -471,21 +506,31 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>0.001040349762079453</v>
+        <v>1.040349762079453</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>0.000536488573490124</v>
+        <v>0.8328166347346401</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -496,66 +541,91 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>0.0004935179472228385</v>
+        <v>0.5587831545305373</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>0.0005428179851395422</v>
+        <v>0.483927998760135</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>21</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>0.0008055585344498605</v>
+        <v>1.097024451113704</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>0.001232033953126148</v>
+        <v>0.6486905807533534</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>0.000536488573490124</v>
+        <v>1.01580091787753</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -563,27 +633,94 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0.0008055585344498605</v>
+        <v>0.8328166347346401</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B16">
+        <v>40</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>0.5587831545305373</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17">
         <v>44</v>
       </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-      <c r="D16">
-        <v>0.001232033953126148</v>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>0.6486905807533534</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>1.07369215070322</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>1.01580091787753</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
     </row>
   </sheetData>
